--- a/Nigeria/Audience Analysis/Audience Comments - Final/Shola_7 Women Will Beg One Man to Marry.xlsx
+++ b/Nigeria/Audience Analysis/Audience Comments - Final/Shola_7 Women Will Beg One Man to Marry.xlsx
@@ -14,11 +14,284 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="269">
+  <si>
+    <t>Segment ID</t>
+  </si>
   <si>
     <t>text</t>
   </si>
   <si>
+    <t>Source URL</t>
+  </si>
+  <si>
+    <t>Reference Text/Context</t>
+  </si>
+  <si>
+    <t>SHO_001</t>
+  </si>
+  <si>
+    <t>SHO_002</t>
+  </si>
+  <si>
+    <t>SHO_003</t>
+  </si>
+  <si>
+    <t>SHO_004</t>
+  </si>
+  <si>
+    <t>SHO_005</t>
+  </si>
+  <si>
+    <t>SHO_006</t>
+  </si>
+  <si>
+    <t>SHO_007</t>
+  </si>
+  <si>
+    <t>SHO_008</t>
+  </si>
+  <si>
+    <t>SHO_009</t>
+  </si>
+  <si>
+    <t>SHO_010</t>
+  </si>
+  <si>
+    <t>SHO_011</t>
+  </si>
+  <si>
+    <t>SHO_012</t>
+  </si>
+  <si>
+    <t>SHO_013</t>
+  </si>
+  <si>
+    <t>SHO_014</t>
+  </si>
+  <si>
+    <t>SHO_015</t>
+  </si>
+  <si>
+    <t>SHO_016</t>
+  </si>
+  <si>
+    <t>SHO_017</t>
+  </si>
+  <si>
+    <t>SHO_018</t>
+  </si>
+  <si>
+    <t>SHO_019</t>
+  </si>
+  <si>
+    <t>SHO_020</t>
+  </si>
+  <si>
+    <t>SHO_021</t>
+  </si>
+  <si>
+    <t>SHO_022</t>
+  </si>
+  <si>
+    <t>SHO_023</t>
+  </si>
+  <si>
+    <t>SHO_024</t>
+  </si>
+  <si>
+    <t>SHO_025</t>
+  </si>
+  <si>
+    <t>SHO_026</t>
+  </si>
+  <si>
+    <t>SHO_027</t>
+  </si>
+  <si>
+    <t>SHO_028</t>
+  </si>
+  <si>
+    <t>SHO_029</t>
+  </si>
+  <si>
+    <t>SHO_030</t>
+  </si>
+  <si>
+    <t>SHO_031</t>
+  </si>
+  <si>
+    <t>SHO_032</t>
+  </si>
+  <si>
+    <t>SHO_033</t>
+  </si>
+  <si>
+    <t>SHO_034</t>
+  </si>
+  <si>
+    <t>SHO_035</t>
+  </si>
+  <si>
+    <t>SHO_036</t>
+  </si>
+  <si>
+    <t>SHO_037</t>
+  </si>
+  <si>
+    <t>SHO_038</t>
+  </si>
+  <si>
+    <t>SHO_039</t>
+  </si>
+  <si>
+    <t>SHO_040</t>
+  </si>
+  <si>
+    <t>SHO_041</t>
+  </si>
+  <si>
+    <t>SHO_042</t>
+  </si>
+  <si>
+    <t>SHO_043</t>
+  </si>
+  <si>
+    <t>SHO_044</t>
+  </si>
+  <si>
+    <t>SHO_045</t>
+  </si>
+  <si>
+    <t>SHO_046</t>
+  </si>
+  <si>
+    <t>SHO_047</t>
+  </si>
+  <si>
+    <t>SHO_048</t>
+  </si>
+  <si>
+    <t>SHO_049</t>
+  </si>
+  <si>
+    <t>SHO_050</t>
+  </si>
+  <si>
+    <t>SHO_051</t>
+  </si>
+  <si>
+    <t>SHO_052</t>
+  </si>
+  <si>
+    <t>SHO_053</t>
+  </si>
+  <si>
+    <t>SHO_054</t>
+  </si>
+  <si>
+    <t>SHO_055</t>
+  </si>
+  <si>
+    <t>SHO_056</t>
+  </si>
+  <si>
+    <t>SHO_057</t>
+  </si>
+  <si>
+    <t>SHO_058</t>
+  </si>
+  <si>
+    <t>SHO_059</t>
+  </si>
+  <si>
+    <t>SHO_060</t>
+  </si>
+  <si>
+    <t>SHO_061</t>
+  </si>
+  <si>
+    <t>SHO_062</t>
+  </si>
+  <si>
+    <t>SHO_063</t>
+  </si>
+  <si>
+    <t>SHO_064</t>
+  </si>
+  <si>
+    <t>SHO_065</t>
+  </si>
+  <si>
+    <t>SHO_066</t>
+  </si>
+  <si>
+    <t>SHO_067</t>
+  </si>
+  <si>
+    <t>SHO_068</t>
+  </si>
+  <si>
+    <t>SHO_069</t>
+  </si>
+  <si>
+    <t>SHO_070</t>
+  </si>
+  <si>
+    <t>SHO_071</t>
+  </si>
+  <si>
+    <t>SHO_072</t>
+  </si>
+  <si>
+    <t>SHO_073</t>
+  </si>
+  <si>
+    <t>SHO_074</t>
+  </si>
+  <si>
+    <t>SHO_075</t>
+  </si>
+  <si>
+    <t>SHO_076</t>
+  </si>
+  <si>
+    <t>SHO_077</t>
+  </si>
+  <si>
+    <t>SHO_078</t>
+  </si>
+  <si>
+    <t>SHO_079</t>
+  </si>
+  <si>
+    <t>SHO_080</t>
+  </si>
+  <si>
+    <t>SHO_081</t>
+  </si>
+  <si>
+    <t>SHO_082</t>
+  </si>
+  <si>
+    <t>SHO_083</t>
+  </si>
+  <si>
+    <t>SHO_084</t>
+  </si>
+  <si>
+    <t>SHO_085</t>
+  </si>
+  <si>
+    <t>SHO_086</t>
+  </si>
+  <si>
+    <t>SHO_087</t>
+  </si>
+  <si>
+    <t>SHO_088</t>
+  </si>
+  <si>
     <t>They go think say na joke. Men are the prize. This girls are just in their era and they feel like all men are after them until they can't even find one. Every man in this world can see a wife to marry no matter how old he is, women can't</t>
   </si>
   <si>
@@ -52,9 +325,6 @@
     <t>That time will be interesting. Already, women are more populous than men. Good value women are just about 20% of total women in the world. Men are wiser as the day goes by. The future of relationship making will be exciting. Relationship coaches will make plenty money</t>
   </si>
   <si>
-    <t>The problem is that there are not many high value men around, so the few of them get all the pussy. Men need to BALL their SACS up !!!!</t>
-  </si>
-  <si>
     <t>Honestly I feel even the men now are getting scared and unwilling to marry lately because of how marriage are being perceived lately and the opposite gender with their stupid wokeness and feminists madness is not helping women.</t>
   </si>
   <si>
@@ -64,12 +334,12 @@
     <t>Men don't want to marry anymore because there's no benefit for them at all</t>
   </si>
   <si>
+    <t>True but 3 women no fit marry wretched man who is equally lazy</t>
+  </si>
+  <si>
     <t>If you are a man building himself right now, realize that you are becoming the most valuable "commodity" on the planet. Don't settle for a woman who just wants your resources. Wait for the one who respects your authority.</t>
   </si>
   <si>
-    <t>True but 3 women no fit marry wretched man who is equally lazy</t>
-  </si>
-  <si>
     <t>Moral of the story: Tell women they don't need men long enough... and they'll end up needing his name so bad they'll pay for the privilege</t>
   </si>
   <si>
@@ -284,13 +554,280 @@
   </si>
   <si>
     <t>True got a text from old friend this morning asking about my wellbeing After everything and she is aware that I'm currently in serious relationship Her word Give me a chance let the Gods will happen No be me una wan use HIV kill that was my tot</t>
+  </si>
+  <si>
+    <t>https://x.com/SohSohchi/status/2030564724279005685</t>
+  </si>
+  <si>
+    <t>https://x.com/Damzyy10/status/2030563203223007334</t>
+  </si>
+  <si>
+    <t>https://x.com/waysofawinner/status/2030579995253555611</t>
+  </si>
+  <si>
+    <t>https://x.com/bucephelandra/status/2030576020999360842</t>
+  </si>
+  <si>
+    <t>https://x.com/starboyzane_/status/2030570335515361520</t>
+  </si>
+  <si>
+    <t>https://x.com/kinanee_samson/status/2030579805234556945</t>
+  </si>
+  <si>
+    <t>https://x.com/RGuntage/status/2030607612295672062</t>
+  </si>
+  <si>
+    <t>https://x.com/G_CobraTheMan/status/2030575907086213213</t>
+  </si>
+  <si>
+    <t>https://x.com/Djbabamillie/status/2030564412466123224</t>
+  </si>
+  <si>
+    <t>https://x.com/Shola_dlb/status/2030588615294615951</t>
+  </si>
+  <si>
+    <t>https://x.com/stcsolutions/status/2030563258847932905</t>
+  </si>
+  <si>
+    <t>https://x.com/Emmyglobal1994/status/2030567917331374111</t>
+  </si>
+  <si>
+    <t>https://x.com/akashmuni27/status/2030649636587995226</t>
+  </si>
+  <si>
+    <t>https://x.com/DapsGiminez/status/2030770473827553611</t>
+  </si>
+  <si>
+    <t>https://x.com/realestfreddy/status/2030596540218114212</t>
+  </si>
+  <si>
+    <t>https://x.com/YoursManfully/status/2030795644483375378</t>
+  </si>
+  <si>
+    <t>https://x.com/MarThun_/status/2030591211656859769</t>
+  </si>
+  <si>
+    <t>https://x.com/kunihira_nick1/status/2030932283708858497</t>
+  </si>
+  <si>
+    <t>https://x.com/Sir_Japh/status/2030588069334720754</t>
+  </si>
+  <si>
+    <t>https://x.com/cringeinthewind/status/2030862471854960835</t>
+  </si>
+  <si>
+    <t>https://x.com/shosssscky/status/2030569718457717063</t>
+  </si>
+  <si>
+    <t>https://x.com/TheDiegoTrombon/status/2030869841423253615</t>
+  </si>
+  <si>
+    <t>https://x.com/itzblackdoll/status/2030603795118330067</t>
+  </si>
+  <si>
+    <t>https://x.com/corona_doge/status/2030639114803130460</t>
+  </si>
+  <si>
+    <t>https://x.com/RickyOnyebuchi/status/2030602173965348953</t>
+  </si>
+  <si>
+    <t>https://x.com/lobistarsfans/status/2030587613925519814</t>
+  </si>
+  <si>
+    <t>https://x.com/sol_Reaper__/status/2030602906345381919</t>
+  </si>
+  <si>
+    <t>https://x.com/lokky_xy/status/2030575584946893033</t>
+  </si>
+  <si>
+    <t>https://x.com/mattiec445804/status/2030619030080434483</t>
+  </si>
+  <si>
+    <t>https://x.com/Notyoursisabeg/status/2030590955024232757</t>
+  </si>
+  <si>
+    <t>https://x.com/SexyJigga66/status/2030575811200233723</t>
+  </si>
+  <si>
+    <t>https://x.com/tobilobaphotog/status/2030565984977735984</t>
+  </si>
+  <si>
+    <t>https://x.com/Abeeb78/status/2030622599307276537</t>
+  </si>
+  <si>
+    <t>https://x.com/SavageJollofina/status/2030646282537115860</t>
+  </si>
+  <si>
+    <t>https://x.com/babayormi/status/2030580528156381666</t>
+  </si>
+  <si>
+    <t>https://x.com/omolaso_/status/2030570784221995484</t>
+  </si>
+  <si>
+    <t>https://x.com/Titilope_khad/status/2030587512880603528</t>
+  </si>
+  <si>
+    <t>https://x.com/AstralMirth/status/2030576108815458798</t>
+  </si>
+  <si>
+    <t>https://x.com/MareyaShamie/status/2030917214484807967</t>
+  </si>
+  <si>
+    <t>https://x.com/ade79677/status/2030575496098963944</t>
+  </si>
+  <si>
+    <t>https://x.com/Genevieveoparah/status/2030697038292107289</t>
+  </si>
+  <si>
+    <t>https://x.com/lolly_pinkii/status/2030563855974150479</t>
+  </si>
+  <si>
+    <t>https://x.com/Vibes_with_Rey/status/2030581427234873441</t>
+  </si>
+  <si>
+    <t>https://x.com/kane_sliq/status/2030594569373458471</t>
+  </si>
+  <si>
+    <t>https://x.com/darazzky/status/2030572285749239986</t>
+  </si>
+  <si>
+    <t>https://x.com/s_v369/status/2030581421425738142</t>
+  </si>
+  <si>
+    <t>https://x.com/HyperGist_/status/2030570926744449198</t>
+  </si>
+  <si>
+    <t>https://x.com/OghCaleb/status/2030567353025491362</t>
+  </si>
+  <si>
+    <t>https://x.com/balogunaliu7/status/2030587711141105984</t>
+  </si>
+  <si>
+    <t>https://x.com/satiq19/status/2030598705112318392</t>
+  </si>
+  <si>
+    <t>https://x.com/DaBitcoinBandi1/status/2030706514294394940</t>
+  </si>
+  <si>
+    <t>https://x.com/__Liberty4All_/status/2030617531132662090</t>
+  </si>
+  <si>
+    <t>https://x.com/JonasSilok26362/status/2030621483194569197</t>
+  </si>
+  <si>
+    <t>https://x.com/5Star_Commando/status/2030589892741231087</t>
+  </si>
+  <si>
+    <t>https://x.com/SmarkRashy/status/2030672556441653379</t>
+  </si>
+  <si>
+    <t>https://x.com/nsafinah82/status/2030579424379150610</t>
+  </si>
+  <si>
+    <t>https://x.com/myshaujean/status/2030598931537617217</t>
+  </si>
+  <si>
+    <t>https://x.com/Victormuster/status/2031419675377029505</t>
+  </si>
+  <si>
+    <t>https://x.com/JoeBlowTheiaft/status/2030610956800143440</t>
+  </si>
+  <si>
+    <t>https://x.com/Oluwasunkanmi0/status/2030585512516366636</t>
+  </si>
+  <si>
+    <t>https://x.com/DB_MOONLIGHT/status/2030926181910843477</t>
+  </si>
+  <si>
+    <t>https://x.com/FuneralBeeze/status/2030763794075402328</t>
+  </si>
+  <si>
+    <t>https://x.com/MasterMind88211/status/2030584477618221403</t>
+  </si>
+  <si>
+    <t>https://x.com/Bigballer91x/status/2030688617530642940</t>
+  </si>
+  <si>
+    <t>https://x.com/Daberrie_/status/2030580528143863857</t>
+  </si>
+  <si>
+    <t>https://x.com/ChArt_LoGicc/status/2030724752071946582</t>
+  </si>
+  <si>
+    <t>https://x.com/PascalDpilot/status/2030730646927142917</t>
+  </si>
+  <si>
+    <t>https://x.com/The_Don_Martinz/status/2030577806535430495</t>
+  </si>
+  <si>
+    <t>https://x.com/KenyanAffi1iate/status/2030623543801835961</t>
+  </si>
+  <si>
+    <t>https://x.com/Humbleanalyst2/status/2030577681721356681</t>
+  </si>
+  <si>
+    <t>https://x.com/daisy_katchy/status/2030627275155104097</t>
+  </si>
+  <si>
+    <t>https://x.com/BillyWilly249/status/2030686127167082627</t>
+  </si>
+  <si>
+    <t>https://x.com/DideeonX/status/2030567892928942520</t>
+  </si>
+  <si>
+    <t>https://x.com/M_Jenist/status/2030572435846697090</t>
+  </si>
+  <si>
+    <t>https://x.com/The_Don_Martinz/status/2030691952379760923</t>
+  </si>
+  <si>
+    <t>https://x.com/24minded/status/2030619586731602037</t>
+  </si>
+  <si>
+    <t>https://x.com/MissakaaPd/status/2030951517566513203</t>
+  </si>
+  <si>
+    <t>https://x.com/SalernoTy91/status/2030742796496257055</t>
+  </si>
+  <si>
+    <t>https://x.com/lilTuneChi96266/status/2030564328366129424</t>
+  </si>
+  <si>
+    <t>https://x.com/OriginalBLKAmer/status/2030620518001582172</t>
+  </si>
+  <si>
+    <t>https://x.com/Cryptosis1_Web3/status/2030589182867837266</t>
+  </si>
+  <si>
+    <t>https://x.com/don_ongo/status/2030676241099948449</t>
+  </si>
+  <si>
+    <t>https://x.com/Dani_D_Maestro/status/2030651109602189604</t>
+  </si>
+  <si>
+    <t>https://x.com/ask_of_keshhh/status/2030571756881064429</t>
+  </si>
+  <si>
+    <t>https://x.com/__Prospero/status/2030654796433084479</t>
+  </si>
+  <si>
+    <t>https://x.com/havefaith07/status/2030582990103826518</t>
+  </si>
+  <si>
+    <t>https://x.com/DynatheBlade/status/2030606189273166200</t>
+  </si>
+  <si>
+    <t>https://x.com/MLT015/status/2030630253614293353</t>
+  </si>
+  <si>
+    <t>https://x.com/itsSh0la/status/2030562648656335258</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,6 +842,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -339,16 +883,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -641,460 +1191,1434 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A90"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
+        <v>39</v>
+      </c>
+      <c r="B37" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
+        <v>42</v>
+      </c>
+      <c r="B40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
+        <v>50</v>
+      </c>
+      <c r="B48" t="s">
+        <v>138</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
+        <v>52</v>
+      </c>
+      <c r="B50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
+        <v>53</v>
+      </c>
+      <c r="B51" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
+        <v>54</v>
+      </c>
+      <c r="B52" t="s">
+        <v>142</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
+        <v>143</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
+        <v>56</v>
+      </c>
+      <c r="B54" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
+        <v>57</v>
+      </c>
+      <c r="B55" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s">
+        <v>146</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
+        <v>60</v>
+      </c>
+      <c r="B58" t="s">
+        <v>148</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
+        <v>61</v>
+      </c>
+      <c r="B59" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
+        <v>62</v>
+      </c>
+      <c r="B60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
+        <v>63</v>
+      </c>
+      <c r="B61" t="s">
+        <v>151</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
+        <v>64</v>
+      </c>
+      <c r="B62" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
+        <v>65</v>
+      </c>
+      <c r="B63" t="s">
+        <v>153</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
+        <v>66</v>
+      </c>
+      <c r="B64" t="s">
+        <v>154</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
+        <v>67</v>
+      </c>
+      <c r="B65" t="s">
+        <v>155</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
+        <v>68</v>
+      </c>
+      <c r="B66" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
+        <v>69</v>
+      </c>
+      <c r="B67" t="s">
+        <v>157</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
+        <v>70</v>
+      </c>
+      <c r="B68" t="s">
+        <v>158</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
+        <v>71</v>
+      </c>
+      <c r="B69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
+        <v>72</v>
+      </c>
+      <c r="B70" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
+        <v>73</v>
+      </c>
+      <c r="B71" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
+        <v>74</v>
+      </c>
+      <c r="B72" t="s">
+        <v>162</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
+        <v>75</v>
+      </c>
+      <c r="B73" t="s">
+        <v>163</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
+        <v>76</v>
+      </c>
+      <c r="B74" t="s">
+        <v>164</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
+        <v>77</v>
+      </c>
+      <c r="B75" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
+        <v>78</v>
+      </c>
+      <c r="B76" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
+        <v>79</v>
+      </c>
+      <c r="B77" t="s">
+        <v>167</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
+        <v>80</v>
+      </c>
+      <c r="B78" t="s">
+        <v>168</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
+        <v>81</v>
+      </c>
+      <c r="B79" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
+        <v>82</v>
+      </c>
+      <c r="B80" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
+        <v>83</v>
+      </c>
+      <c r="B81" t="s">
+        <v>171</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
+        <v>84</v>
+      </c>
+      <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
+        <v>85</v>
+      </c>
+      <c r="B83" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
+        <v>86</v>
+      </c>
+      <c r="B84" t="s">
+        <v>174</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
+        <v>87</v>
+      </c>
+      <c r="B85" t="s">
+        <v>175</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
+        <v>88</v>
+      </c>
+      <c r="B86" t="s">
+        <v>176</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
+        <v>89</v>
+      </c>
+      <c r="B87" t="s">
+        <v>177</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
+        <v>90</v>
+      </c>
+      <c r="B88" t="s">
+        <v>178</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="B89" t="s">
+        <v>179</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="D2" r:id="rId2"/>
+    <hyperlink ref="C3" r:id="rId3"/>
+    <hyperlink ref="D3" r:id="rId4"/>
+    <hyperlink ref="C4" r:id="rId5"/>
+    <hyperlink ref="D4" r:id="rId6"/>
+    <hyperlink ref="C5" r:id="rId7"/>
+    <hyperlink ref="D5" r:id="rId8"/>
+    <hyperlink ref="C6" r:id="rId9"/>
+    <hyperlink ref="D6" r:id="rId10"/>
+    <hyperlink ref="C7" r:id="rId11"/>
+    <hyperlink ref="D7" r:id="rId12"/>
+    <hyperlink ref="C8" r:id="rId13"/>
+    <hyperlink ref="D8" r:id="rId14"/>
+    <hyperlink ref="C9" r:id="rId15"/>
+    <hyperlink ref="D9" r:id="rId16"/>
+    <hyperlink ref="C10" r:id="rId17"/>
+    <hyperlink ref="D10" r:id="rId18"/>
+    <hyperlink ref="C11" r:id="rId19"/>
+    <hyperlink ref="D11" r:id="rId20"/>
+    <hyperlink ref="C12" r:id="rId21"/>
+    <hyperlink ref="D12" r:id="rId22"/>
+    <hyperlink ref="C13" r:id="rId23"/>
+    <hyperlink ref="D13" r:id="rId24"/>
+    <hyperlink ref="C14" r:id="rId25"/>
+    <hyperlink ref="D14" r:id="rId26"/>
+    <hyperlink ref="C15" r:id="rId27"/>
+    <hyperlink ref="D15" r:id="rId28"/>
+    <hyperlink ref="C16" r:id="rId29"/>
+    <hyperlink ref="D16" r:id="rId30"/>
+    <hyperlink ref="C17" r:id="rId31"/>
+    <hyperlink ref="D17" r:id="rId32"/>
+    <hyperlink ref="C18" r:id="rId33"/>
+    <hyperlink ref="D18" r:id="rId34"/>
+    <hyperlink ref="C19" r:id="rId35"/>
+    <hyperlink ref="D19" r:id="rId36"/>
+    <hyperlink ref="C20" r:id="rId37"/>
+    <hyperlink ref="D20" r:id="rId38"/>
+    <hyperlink ref="C21" r:id="rId39"/>
+    <hyperlink ref="D21" r:id="rId40"/>
+    <hyperlink ref="C22" r:id="rId41"/>
+    <hyperlink ref="D22" r:id="rId42"/>
+    <hyperlink ref="C23" r:id="rId43"/>
+    <hyperlink ref="D23" r:id="rId44"/>
+    <hyperlink ref="C24" r:id="rId45"/>
+    <hyperlink ref="D24" r:id="rId46"/>
+    <hyperlink ref="C25" r:id="rId47"/>
+    <hyperlink ref="D25" r:id="rId48"/>
+    <hyperlink ref="C26" r:id="rId49"/>
+    <hyperlink ref="D26" r:id="rId50"/>
+    <hyperlink ref="C27" r:id="rId51"/>
+    <hyperlink ref="D27" r:id="rId52"/>
+    <hyperlink ref="C28" r:id="rId53"/>
+    <hyperlink ref="D28" r:id="rId54"/>
+    <hyperlink ref="C29" r:id="rId55"/>
+    <hyperlink ref="D29" r:id="rId56"/>
+    <hyperlink ref="C30" r:id="rId57"/>
+    <hyperlink ref="D30" r:id="rId58"/>
+    <hyperlink ref="C31" r:id="rId59"/>
+    <hyperlink ref="D31" r:id="rId60"/>
+    <hyperlink ref="C32" r:id="rId61"/>
+    <hyperlink ref="D32" r:id="rId62"/>
+    <hyperlink ref="C33" r:id="rId63"/>
+    <hyperlink ref="D33" r:id="rId64"/>
+    <hyperlink ref="C34" r:id="rId65"/>
+    <hyperlink ref="D34" r:id="rId66"/>
+    <hyperlink ref="C35" r:id="rId67"/>
+    <hyperlink ref="D35" r:id="rId68"/>
+    <hyperlink ref="C36" r:id="rId69"/>
+    <hyperlink ref="D36" r:id="rId70"/>
+    <hyperlink ref="C37" r:id="rId71"/>
+    <hyperlink ref="D37" r:id="rId72"/>
+    <hyperlink ref="C38" r:id="rId73"/>
+    <hyperlink ref="D38" r:id="rId74"/>
+    <hyperlink ref="C39" r:id="rId75"/>
+    <hyperlink ref="D39" r:id="rId76"/>
+    <hyperlink ref="C40" r:id="rId77"/>
+    <hyperlink ref="D40" r:id="rId78"/>
+    <hyperlink ref="C41" r:id="rId79"/>
+    <hyperlink ref="D41" r:id="rId80"/>
+    <hyperlink ref="C42" r:id="rId81"/>
+    <hyperlink ref="D42" r:id="rId82"/>
+    <hyperlink ref="C43" r:id="rId83"/>
+    <hyperlink ref="D43" r:id="rId84"/>
+    <hyperlink ref="C44" r:id="rId85"/>
+    <hyperlink ref="D44" r:id="rId86"/>
+    <hyperlink ref="C45" r:id="rId87"/>
+    <hyperlink ref="D45" r:id="rId88"/>
+    <hyperlink ref="C46" r:id="rId89"/>
+    <hyperlink ref="D46" r:id="rId90"/>
+    <hyperlink ref="C47" r:id="rId91"/>
+    <hyperlink ref="D47" r:id="rId92"/>
+    <hyperlink ref="C48" r:id="rId93"/>
+    <hyperlink ref="D48" r:id="rId94"/>
+    <hyperlink ref="C49" r:id="rId95"/>
+    <hyperlink ref="D49" r:id="rId96"/>
+    <hyperlink ref="C50" r:id="rId97"/>
+    <hyperlink ref="D50" r:id="rId98"/>
+    <hyperlink ref="C51" r:id="rId99"/>
+    <hyperlink ref="D51" r:id="rId100"/>
+    <hyperlink ref="C52" r:id="rId101"/>
+    <hyperlink ref="D52" r:id="rId102"/>
+    <hyperlink ref="C53" r:id="rId103"/>
+    <hyperlink ref="D53" r:id="rId104"/>
+    <hyperlink ref="C54" r:id="rId105"/>
+    <hyperlink ref="D54" r:id="rId106"/>
+    <hyperlink ref="C55" r:id="rId107"/>
+    <hyperlink ref="D55" r:id="rId108"/>
+    <hyperlink ref="C56" r:id="rId109"/>
+    <hyperlink ref="D56" r:id="rId110"/>
+    <hyperlink ref="C57" r:id="rId111"/>
+    <hyperlink ref="D57" r:id="rId112"/>
+    <hyperlink ref="C58" r:id="rId113"/>
+    <hyperlink ref="D58" r:id="rId114"/>
+    <hyperlink ref="C59" r:id="rId115"/>
+    <hyperlink ref="D59" r:id="rId116"/>
+    <hyperlink ref="C60" r:id="rId117"/>
+    <hyperlink ref="D60" r:id="rId118"/>
+    <hyperlink ref="C61" r:id="rId119"/>
+    <hyperlink ref="D61" r:id="rId120"/>
+    <hyperlink ref="C62" r:id="rId121"/>
+    <hyperlink ref="D62" r:id="rId122"/>
+    <hyperlink ref="C63" r:id="rId123"/>
+    <hyperlink ref="D63" r:id="rId124"/>
+    <hyperlink ref="C64" r:id="rId125"/>
+    <hyperlink ref="D64" r:id="rId126"/>
+    <hyperlink ref="C65" r:id="rId127"/>
+    <hyperlink ref="D65" r:id="rId128"/>
+    <hyperlink ref="C66" r:id="rId129"/>
+    <hyperlink ref="D66" r:id="rId130"/>
+    <hyperlink ref="C67" r:id="rId131"/>
+    <hyperlink ref="D67" r:id="rId132"/>
+    <hyperlink ref="C68" r:id="rId133"/>
+    <hyperlink ref="D68" r:id="rId134"/>
+    <hyperlink ref="C69" r:id="rId135"/>
+    <hyperlink ref="D69" r:id="rId136"/>
+    <hyperlink ref="C70" r:id="rId137"/>
+    <hyperlink ref="D70" r:id="rId138"/>
+    <hyperlink ref="C71" r:id="rId139"/>
+    <hyperlink ref="D71" r:id="rId140"/>
+    <hyperlink ref="C72" r:id="rId141"/>
+    <hyperlink ref="D72" r:id="rId142"/>
+    <hyperlink ref="C73" r:id="rId143"/>
+    <hyperlink ref="D73" r:id="rId144"/>
+    <hyperlink ref="C74" r:id="rId145"/>
+    <hyperlink ref="D74" r:id="rId146"/>
+    <hyperlink ref="C75" r:id="rId147"/>
+    <hyperlink ref="D75" r:id="rId148"/>
+    <hyperlink ref="C76" r:id="rId149"/>
+    <hyperlink ref="D76" r:id="rId150"/>
+    <hyperlink ref="C77" r:id="rId151"/>
+    <hyperlink ref="D77" r:id="rId152"/>
+    <hyperlink ref="C78" r:id="rId153"/>
+    <hyperlink ref="D78" r:id="rId154"/>
+    <hyperlink ref="C79" r:id="rId155"/>
+    <hyperlink ref="D79" r:id="rId156"/>
+    <hyperlink ref="C80" r:id="rId157"/>
+    <hyperlink ref="D80" r:id="rId158"/>
+    <hyperlink ref="C81" r:id="rId159"/>
+    <hyperlink ref="D81" r:id="rId160"/>
+    <hyperlink ref="C82" r:id="rId161"/>
+    <hyperlink ref="D82" r:id="rId162"/>
+    <hyperlink ref="C83" r:id="rId163"/>
+    <hyperlink ref="D83" r:id="rId164"/>
+    <hyperlink ref="C84" r:id="rId165"/>
+    <hyperlink ref="D84" r:id="rId166"/>
+    <hyperlink ref="C85" r:id="rId167"/>
+    <hyperlink ref="D85" r:id="rId168"/>
+    <hyperlink ref="C86" r:id="rId169"/>
+    <hyperlink ref="D86" r:id="rId170"/>
+    <hyperlink ref="C87" r:id="rId171"/>
+    <hyperlink ref="D87" r:id="rId172"/>
+    <hyperlink ref="C88" r:id="rId173"/>
+    <hyperlink ref="D88" r:id="rId174"/>
+    <hyperlink ref="C89" r:id="rId175"/>
+    <hyperlink ref="D89" r:id="rId176"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>